--- a/public/Menu.xlsx
+++ b/public/Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00727C37-1B67-4C61-A5BE-AFFBE2ACBB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AC6A68-4A07-4D0C-9C7A-3594170A3771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="207">
   <si>
     <t>Category</t>
   </si>
@@ -638,6 +638,9 @@
   </si>
   <si>
     <t>Sweets &amp; Dessert</t>
+  </si>
+  <si>
+    <t>Loita Fish</t>
   </si>
 </sst>
 </file>
@@ -769,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -802,9 +805,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1107,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D196"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1405,10 +1405,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="C25" s="3">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1416,10 +1416,10 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C26" s="3">
-        <v>18.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1427,10 +1427,10 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="3">
-        <v>5.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -1438,7 +1438,7 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C28" s="3">
         <v>5.99</v>
@@ -1449,10 +1449,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C29" s="3">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -1460,10 +1460,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C30" s="3">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -1471,10 +1471,10 @@
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3">
-        <v>12.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1482,10 +1482,10 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3">
-        <v>7.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1493,10 +1493,10 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C33" s="3">
-        <v>12.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1504,21 +1504,21 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C34" s="3">
-        <v>15.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C35" s="3">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1526,10 +1526,10 @@
         <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C36" s="3">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1537,10 +1537,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C37" s="3">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1548,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C38" s="3">
         <v>6.99</v>
@@ -1559,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C39" s="3">
         <v>6.99</v>
@@ -1570,10 +1570,10 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C40" s="3">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1581,10 +1581,10 @@
         <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C41" s="3">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1592,10 +1592,10 @@
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C42" s="3">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1603,10 +1603,10 @@
         <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C43" s="3">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1614,10 +1614,10 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C44" s="3">
-        <v>17.989999999999998</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -1625,10 +1625,10 @@
         <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C45" s="3">
-        <v>15.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -1636,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C46" s="3">
         <v>15.99</v>
@@ -1647,10 +1647,10 @@
         <v>7</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C47" s="3">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -1658,10 +1658,10 @@
         <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C48" s="3">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1669,10 +1669,10 @@
         <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C49" s="3">
-        <v>11.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1680,10 +1680,10 @@
         <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C50" s="3">
-        <v>13.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1691,10 +1691,10 @@
         <v>7</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C51" s="3">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -1702,32 +1702,32 @@
         <v>7</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C52" s="3">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>8</v>
+        <v>183</v>
       </c>
       <c r="C53" s="3">
-        <v>16.989999999999998</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C54" s="5">
-        <v>6.49</v>
+      <c r="B54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="3">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -1735,20 +1735,20 @@
         <v>11</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C55" s="5">
-        <v>5.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56">
+      <c r="B56" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="5">
         <v>5.99</v>
       </c>
     </row>
@@ -1757,21 +1757,21 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C57">
         <v>5.99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>16</v>
+      <c r="A58" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>186</v>
+        <v>10</v>
       </c>
       <c r="C58">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1779,10 +1779,10 @@
         <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C59">
-        <v>19.989999999999998</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1790,10 +1790,10 @@
         <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="C60">
-        <v>6.49</v>
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1801,10 +1801,10 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>8.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1812,10 +1812,10 @@
         <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C62">
-        <v>6.49</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1823,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63">
         <v>6.49</v>
@@ -1834,21 +1834,21 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64">
-        <v>3.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>10.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1856,10 +1856,10 @@
         <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C66">
-        <v>4.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1867,10 +1867,10 @@
         <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C67">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1878,20 +1878,20 @@
         <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C68">
-        <v>4.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" s="7">
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69">
         <v>4.99</v>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
         <v>23</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C70" s="7">
         <v>4.99</v>
@@ -1908,13 +1908,13 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C71" s="7">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>30</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C72" s="7">
         <v>3.99</v>
@@ -1933,7 +1933,7 @@
         <v>30</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="C73" s="7">
         <v>3.99</v>
@@ -1944,7 +1944,7 @@
         <v>30</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C74" s="7">
         <v>3.99</v>
@@ -1955,32 +1955,32 @@
         <v>30</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C75" s="7">
         <v>3.99</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="9">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B76" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C76" s="7">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77">
-        <v>3.99</v>
+      <c r="B77" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="9">
+        <v>5.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1988,10 +1988,10 @@
         <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C78">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1999,21 +1999,21 @@
         <v>30</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C79">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C80">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -2021,10 +2021,10 @@
         <v>46</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -2032,7 +2032,7 @@
         <v>46</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C82">
         <v>4.99</v>
@@ -2043,7 +2043,7 @@
         <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C83">
         <v>4.99</v>
@@ -2054,7 +2054,7 @@
         <v>46</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C84">
         <v>4.99</v>
@@ -2065,7 +2065,7 @@
         <v>46</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C85">
         <v>4.99</v>
@@ -2076,10 +2076,10 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C86">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -2087,7 +2087,7 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C87">
         <v>5.99</v>
@@ -2095,13 +2095,13 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C88">
-        <v>26.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -2109,7 +2109,7 @@
         <v>191</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C89">
         <v>26.99</v>
@@ -2120,10 +2120,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C90">
-        <v>16.989999999999998</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -2131,10 +2131,10 @@
         <v>191</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C91">
-        <v>22.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -2142,10 +2142,10 @@
         <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C92">
-        <v>6.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -2153,7 +2153,7 @@
         <v>191</v>
       </c>
       <c r="B93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C93">
         <v>6.99</v>
@@ -2164,21 +2164,21 @@
         <v>191</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C94">
-        <v>6.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="B95" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C95">
-        <v>3.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -2186,10 +2186,10 @@
         <v>66</v>
       </c>
       <c r="B96" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C96">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -2197,7 +2197,7 @@
         <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="C97">
         <v>6.99</v>
@@ -2208,10 +2208,10 @@
         <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C98">
-        <v>9.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -2219,10 +2219,10 @@
         <v>66</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="C99">
-        <v>84.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -2230,10 +2230,10 @@
         <v>66</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C100">
-        <v>17.989999999999998</v>
+        <v>84.99</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -2241,10 +2241,10 @@
         <v>66</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C101">
-        <v>6.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -2252,10 +2252,10 @@
         <v>66</v>
       </c>
       <c r="B102" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C102">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -2263,10 +2263,10 @@
         <v>66</v>
       </c>
       <c r="B103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C103">
-        <v>2.4900000000000002</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -2274,10 +2274,10 @@
         <v>66</v>
       </c>
       <c r="B104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C104">
-        <v>4.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -2285,10 +2285,10 @@
         <v>66</v>
       </c>
       <c r="B105" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C105">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -2296,10 +2296,10 @@
         <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C106">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -2307,10 +2307,10 @@
         <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C107">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -2318,10 +2318,10 @@
         <v>66</v>
       </c>
       <c r="B108" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C108">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -2329,10 +2329,10 @@
         <v>66</v>
       </c>
       <c r="B109" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C109">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -2340,7 +2340,7 @@
         <v>66</v>
       </c>
       <c r="B110" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C110">
         <v>1.99</v>
@@ -2351,7 +2351,7 @@
         <v>66</v>
       </c>
       <c r="B111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C111">
         <v>1.99</v>
@@ -2362,10 +2362,10 @@
         <v>66</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="C112">
-        <v>6.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2373,10 +2373,10 @@
         <v>66</v>
       </c>
       <c r="B113" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="C113">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -2384,10 +2384,10 @@
         <v>66</v>
       </c>
       <c r="B114" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C114">
-        <v>5.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -2395,10 +2395,10 @@
         <v>66</v>
       </c>
       <c r="B115" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C115">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -2406,10 +2406,10 @@
         <v>66</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C116">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -2417,10 +2417,10 @@
         <v>66</v>
       </c>
       <c r="B117" t="s">
-        <v>194</v>
+        <v>65</v>
       </c>
       <c r="C117">
-        <v>9.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -2428,10 +2428,10 @@
         <v>66</v>
       </c>
       <c r="B118" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C118">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -2439,21 +2439,21 @@
         <v>66</v>
       </c>
       <c r="B119" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C119">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="B120" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C120">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -2461,10 +2461,10 @@
         <v>198</v>
       </c>
       <c r="B121" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="C121">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -2472,10 +2472,10 @@
         <v>198</v>
       </c>
       <c r="B122" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C122">
-        <v>0.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -2483,10 +2483,10 @@
         <v>198</v>
       </c>
       <c r="B123" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C123">
-        <v>3.99</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -2494,10 +2494,10 @@
         <v>198</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C124">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -2505,10 +2505,10 @@
         <v>198</v>
       </c>
       <c r="B125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C125">
-        <v>4.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -2516,7 +2516,7 @@
         <v>198</v>
       </c>
       <c r="B126" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C126">
         <v>4.49</v>
@@ -2527,21 +2527,21 @@
         <v>198</v>
       </c>
       <c r="B127" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C127">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B128" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C128">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -2549,7 +2549,7 @@
         <v>110</v>
       </c>
       <c r="B129" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C129">
         <v>6.99</v>
@@ -2560,7 +2560,7 @@
         <v>110</v>
       </c>
       <c r="B130" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C130">
         <v>6.99</v>
@@ -2571,10 +2571,10 @@
         <v>110</v>
       </c>
       <c r="B131" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C131">
-        <v>8.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2582,10 +2582,10 @@
         <v>110</v>
       </c>
       <c r="B132" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C132">
-        <v>7.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2593,7 +2593,7 @@
         <v>110</v>
       </c>
       <c r="B133" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C133">
         <v>7.99</v>
@@ -2604,7 +2604,7 @@
         <v>110</v>
       </c>
       <c r="B134" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C134">
         <v>7.99</v>
@@ -2615,10 +2615,10 @@
         <v>110</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C135">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -2626,10 +2626,10 @@
         <v>110</v>
       </c>
       <c r="B136" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C136">
-        <v>3.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -2637,10 +2637,10 @@
         <v>110</v>
       </c>
       <c r="B137" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="C137">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -2648,10 +2648,10 @@
         <v>110</v>
       </c>
       <c r="B138" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="C138">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -2659,10 +2659,10 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C139">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -2670,7 +2670,7 @@
         <v>110</v>
       </c>
       <c r="B140" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C140">
         <v>2.99</v>
@@ -2681,10 +2681,10 @@
         <v>110</v>
       </c>
       <c r="B141" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C141">
-        <v>5.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -2692,10 +2692,10 @@
         <v>110</v>
       </c>
       <c r="B142" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C142">
-        <v>2.59</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -2703,7 +2703,7 @@
         <v>110</v>
       </c>
       <c r="B143" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C143">
         <v>2.59</v>
@@ -2714,7 +2714,7 @@
         <v>110</v>
       </c>
       <c r="B144" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C144">
         <v>2.59</v>
@@ -2725,7 +2725,7 @@
         <v>110</v>
       </c>
       <c r="B145" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C145">
         <v>2.59</v>
@@ -2736,7 +2736,7 @@
         <v>110</v>
       </c>
       <c r="B146" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C146">
         <v>2.59</v>
@@ -2758,7 +2758,7 @@
         <v>110</v>
       </c>
       <c r="B148" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C148">
         <v>2.59</v>
@@ -2769,7 +2769,7 @@
         <v>110</v>
       </c>
       <c r="B149" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C149">
         <v>2.59</v>
@@ -2780,10 +2780,10 @@
         <v>110</v>
       </c>
       <c r="B150" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C150">
-        <v>3.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
@@ -2791,10 +2791,10 @@
         <v>110</v>
       </c>
       <c r="B151" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C151">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
         <v>110</v>
       </c>
       <c r="B152" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C152">
         <v>2.59</v>
@@ -2813,10 +2813,10 @@
         <v>110</v>
       </c>
       <c r="B153" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C153">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -2824,10 +2824,10 @@
         <v>110</v>
       </c>
       <c r="B154" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C154">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -2835,7 +2835,7 @@
         <v>110</v>
       </c>
       <c r="B155" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C155">
         <v>2.59</v>
@@ -2846,7 +2846,7 @@
         <v>110</v>
       </c>
       <c r="B156" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C156">
         <v>2.59</v>
@@ -2857,10 +2857,10 @@
         <v>110</v>
       </c>
       <c r="B157" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C157">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -2868,10 +2868,10 @@
         <v>110</v>
       </c>
       <c r="B158" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C158">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -2879,10 +2879,10 @@
         <v>110</v>
       </c>
       <c r="B159" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C159">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -2890,7 +2890,7 @@
         <v>110</v>
       </c>
       <c r="B160" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C160">
         <v>1.99</v>
@@ -2901,10 +2901,10 @@
         <v>110</v>
       </c>
       <c r="B161" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C161">
-        <v>3.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -2912,10 +2912,10 @@
         <v>110</v>
       </c>
       <c r="B162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C162">
-        <v>5.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -2923,10 +2923,10 @@
         <v>110</v>
       </c>
       <c r="B163" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C163">
-        <v>2.59</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -2934,7 +2934,7 @@
         <v>110</v>
       </c>
       <c r="B164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C164">
         <v>2.59</v>
@@ -2945,7 +2945,7 @@
         <v>110</v>
       </c>
       <c r="B165" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C165">
         <v>2.59</v>
@@ -2953,13 +2953,13 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B166" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C166">
-        <v>9.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -2967,10 +2967,10 @@
         <v>133</v>
       </c>
       <c r="B167" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C167">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -2978,10 +2978,10 @@
         <v>133</v>
       </c>
       <c r="B168" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C168">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -2989,10 +2989,10 @@
         <v>133</v>
       </c>
       <c r="B169" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C169">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -3000,10 +3000,10 @@
         <v>133</v>
       </c>
       <c r="B170" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C170">
-        <v>4.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -3011,10 +3011,10 @@
         <v>133</v>
       </c>
       <c r="B171" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C171">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -3022,10 +3022,10 @@
         <v>133</v>
       </c>
       <c r="B172" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C172">
-        <v>2.4900000000000002</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -3033,10 +3033,10 @@
         <v>133</v>
       </c>
       <c r="B173" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C173">
-        <v>3.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -3044,7 +3044,7 @@
         <v>133</v>
       </c>
       <c r="B174" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C174">
         <v>3.99</v>
@@ -3055,10 +3055,10 @@
         <v>133</v>
       </c>
       <c r="B175" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C175">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -3066,10 +3066,10 @@
         <v>133</v>
       </c>
       <c r="B176" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C176">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -3077,10 +3077,10 @@
         <v>133</v>
       </c>
       <c r="B177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C177">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -3088,10 +3088,10 @@
         <v>133</v>
       </c>
       <c r="B178" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C178">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -3099,10 +3099,10 @@
         <v>133</v>
       </c>
       <c r="B179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C179">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -3110,10 +3110,10 @@
         <v>133</v>
       </c>
       <c r="B180" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C180">
-        <v>1.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -3121,7 +3121,7 @@
         <v>133</v>
       </c>
       <c r="B181" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C181">
         <v>1.99</v>
@@ -3132,10 +3132,10 @@
         <v>133</v>
       </c>
       <c r="B182" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C182">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
@@ -3143,7 +3143,7 @@
         <v>133</v>
       </c>
       <c r="B183" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C183">
         <v>4.49</v>
@@ -3154,10 +3154,10 @@
         <v>133</v>
       </c>
       <c r="B184" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C184">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -3165,10 +3165,10 @@
         <v>133</v>
       </c>
       <c r="B185" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C185">
-        <v>5.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -3176,10 +3176,10 @@
         <v>133</v>
       </c>
       <c r="B186" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C186">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -3187,97 +3187,108 @@
         <v>133</v>
       </c>
       <c r="B187" t="s">
+        <v>131</v>
+      </c>
+      <c r="C187">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B188" t="s">
         <v>132</v>
       </c>
-      <c r="C187">
+      <c r="C188">
         <v>4.99</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="14" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B189" t="s">
         <v>200</v>
       </c>
-      <c r="C188">
+      <c r="C189">
         <v>5.99</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="14" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B190" t="s">
         <v>201</v>
       </c>
-      <c r="C189">
+      <c r="C190">
         <v>9.99</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="14" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B191" t="s">
         <v>202</v>
       </c>
-      <c r="C190">
+      <c r="C191">
         <v>3.49</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="14" t="s">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B192" t="s">
         <v>141</v>
-      </c>
-      <c r="C191">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="B192" t="s">
-        <v>204</v>
       </c>
       <c r="C192">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="14" t="s">
+      <c r="A193" s="4" t="s">
         <v>205</v>
       </c>
       <c r="B193" t="s">
+        <v>204</v>
+      </c>
+      <c r="C193">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B194" t="s">
         <v>134</v>
       </c>
-      <c r="C193">
+      <c r="C194">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="14" t="s">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B195" t="s">
         <v>135</v>
       </c>
-      <c r="C194">
+      <c r="C195">
         <v>20.99</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="14" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B196" t="s">
         <v>136</v>
       </c>
-      <c r="C195">
+      <c r="C196">
         <v>16.989999999999998</v>
       </c>
     </row>

--- a/public/Menu.xlsx
+++ b/public/Menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AC6A68-4A07-4D0C-9C7A-3594170A3771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76649709-73EA-43C2-A12F-22045A17EBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="206">
   <si>
     <t>Category</t>
   </si>
@@ -34,12 +34,6 @@
     <t>Koral Fish (Steak - head&amp;tail excluded) - 2lb</t>
   </si>
   <si>
-    <t>Shoil Fish Fish (Steak - head&amp;tail excluded) - 2lb</t>
-  </si>
-  <si>
-    <t>Dima Icha (Shrimp with head &amp; Egg) - 250gm</t>
-  </si>
-  <si>
     <t>Frozen Fish</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>PLAIN PARATHA 30PACK</t>
   </si>
   <si>
-    <t>Naga Singara</t>
-  </si>
-  <si>
     <t>Vegetable Singara Family Pack (25 Pieces)</t>
   </si>
   <si>
@@ -109,9 +100,6 @@
     <t>Dal er bori 300gm</t>
   </si>
   <si>
-    <t>Frozen Satkora</t>
-  </si>
-  <si>
     <t>Frozen Vegetables</t>
   </si>
   <si>
@@ -151,24 +139,12 @@
     <t>Nicobena Mix Pickle</t>
   </si>
   <si>
-    <t>Nicobena Mango Pickle</t>
-  </si>
-  <si>
     <t>Nicobina Tetul Pickle</t>
   </si>
   <si>
-    <t>Nicobina Garlic Pickle 220gm</t>
-  </si>
-  <si>
     <t>Pickle &amp; Chutney</t>
   </si>
   <si>
-    <t>Laccha Semai 200gm</t>
-  </si>
-  <si>
-    <t>Bombay Laccha Semai 350gm</t>
-  </si>
-  <si>
     <t>Nido Milk Powder 2500gm</t>
   </si>
   <si>
@@ -181,9 +157,6 @@
     <t>Tetul Paste</t>
   </si>
   <si>
-    <t>ACI Stick Noodles 180gm</t>
-  </si>
-  <si>
     <t>Nurjahan Paan Masala</t>
   </si>
   <si>
@@ -436,9 +409,6 @@
     <t>Khejur Gur 500gm</t>
   </si>
   <si>
-    <t>Sale Price</t>
-  </si>
-  <si>
     <t>Balachao</t>
   </si>
   <si>
@@ -448,30 +418,15 @@
     <t>Baghabari Ghee 450gm</t>
   </si>
   <si>
-    <t>Specials</t>
-  </si>
-  <si>
     <t>RUI FISH (2KG+) - Cut</t>
   </si>
   <si>
     <t>Rui Fish 3KG+ (Cut &amp; Desclaed)</t>
   </si>
   <si>
-    <t>Rui Fish 5KG+ - Cut</t>
-  </si>
-  <si>
-    <t>Ayer Fish (1.5KG+) - Cut</t>
-  </si>
-  <si>
-    <t>Boal Fish (2KG+) - Cut</t>
-  </si>
-  <si>
     <t>Chitol Fish (2/3KG) - Cut</t>
   </si>
   <si>
-    <t>Mrigel 3KG+ (Cut &amp; Desclaed)</t>
-  </si>
-  <si>
     <t>Hilsha Fish 1000gm++ - Cut</t>
   </si>
   <si>
@@ -496,9 +451,6 @@
     <t xml:space="preserve">Koi Fish 250gm </t>
   </si>
   <si>
-    <t xml:space="preserve">Koi Fish 1KG </t>
-  </si>
-  <si>
     <t>Keski Fish 250gm</t>
   </si>
   <si>
@@ -541,9 +493,6 @@
     <t>Ground Beef (approx. 1lb Pack)</t>
   </si>
   <si>
-    <t>Beef Nalli (3/4lb Pack)</t>
-  </si>
-  <si>
     <t>Hard Chicken (Medium Size)</t>
   </si>
   <si>
@@ -571,9 +520,6 @@
     <t>Lamb Leg - (whole) - Local</t>
   </si>
   <si>
-    <t>Mutton (Goat) - Kacchi Cut - Imported</t>
-  </si>
-  <si>
     <t>Chepa Shutki</t>
   </si>
   <si>
@@ -637,10 +583,61 @@
     <t>Premium Sweets - Khirsha Doi</t>
   </si>
   <si>
-    <t>Sweets &amp; Dessert</t>
-  </si>
-  <si>
-    <t>Loita Fish</t>
+    <t>Rui Fish 5KG+ - Cut (Can be taken full or half)</t>
+  </si>
+  <si>
+    <t>Katla Fish 5KG+ - Cut (Can be taken full or half)</t>
+  </si>
+  <si>
+    <t>Ayer 3KG+ - Cut</t>
+  </si>
+  <si>
+    <t>River Pangash Fish (3KG+) - Cut</t>
+  </si>
+  <si>
+    <t>Mixed Fish 250gm</t>
+  </si>
+  <si>
+    <t>Baila Fish 500gm</t>
+  </si>
+  <si>
+    <t>Meni Fish 500gm</t>
+  </si>
+  <si>
+    <t>Fresh Vegetables &amp; Fruits</t>
+  </si>
+  <si>
+    <t>Potol</t>
+  </si>
+  <si>
+    <t>Fazli Aam</t>
+  </si>
+  <si>
+    <t>Zara Lebu</t>
+  </si>
+  <si>
+    <t>Premium Sweets - Assorted Laddu</t>
+  </si>
+  <si>
+    <t>Golda Chingri Bhuna 500gm</t>
+  </si>
+  <si>
+    <t>Masoor Dal 4lb</t>
+  </si>
+  <si>
+    <t>Moong Dal 4lb</t>
+  </si>
+  <si>
+    <t>Red Chira (Flatten Rice) 900gm</t>
+  </si>
+  <si>
+    <t>Cocola Noodles</t>
+  </si>
+  <si>
+    <t>Hot Chanachur</t>
+  </si>
+  <si>
+    <t>Deshi Sweets</t>
   </si>
 </sst>
 </file>
@@ -650,7 +647,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -665,8 +662,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -679,14 +683,8 @@
         <bgColor rgb="FF667EEA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -768,11 +766,500 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -786,25 +1273,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1111,2186 +1664,2156 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>138</v>
-      </c>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="3">
-        <v>10.99</v>
-      </c>
-      <c r="D2" s="3">
-        <v>8.99</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="8">
+        <v>24.99</v>
+      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="3">
-        <v>12.99</v>
-      </c>
-      <c r="D3" s="3">
-        <v>7.99</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="8">
+        <v>42.99</v>
+      </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="3">
-        <v>7.99</v>
-      </c>
-      <c r="D4" s="3">
-        <v>6.99</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="8">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="3">
-        <v>6.99</v>
-      </c>
-      <c r="D5" s="3">
-        <v>5.99</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="8">
+        <v>89.99</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="3">
-        <v>7.99</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="8">
+        <v>10.99</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="3">
-        <v>19.989999999999998</v>
-      </c>
-      <c r="D7" s="3">
-        <v>16.989999999999998</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="8">
+        <v>54.99</v>
+      </c>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="3">
-        <v>24.99</v>
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="8">
+        <v>32.99</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="3">
-        <v>42.99</v>
+        <v>4</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="8">
+        <v>37.99</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="3">
-        <v>79.989999999999995</v>
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="8">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="3">
-        <v>24.99</v>
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="8">
+        <v>26.99</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="3">
-        <v>34.99</v>
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="8">
+        <v>12.99</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="3">
-        <v>54.99</v>
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="8">
+        <v>13.99</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="3">
-        <v>48.99</v>
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="8">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="3">
-        <v>37.99</v>
+        <v>4</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5.99</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="3">
-        <v>16.989999999999998</v>
+        <v>4</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="8">
+        <v>12.99</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="3">
-        <v>26.99</v>
+        <v>4</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5.99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="3">
-        <v>12.99</v>
+        <v>4</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="8">
+        <v>13.99</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="3">
-        <v>13.99</v>
+        <v>4</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="8">
+        <v>6.99</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="3">
-        <v>16.989999999999998</v>
+        <v>4</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="8">
+        <v>12.99</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="3">
-        <v>17.989999999999998</v>
+      <c r="B21" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="8">
+        <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="3">
-        <v>8.99</v>
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="8">
+        <v>5.99</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="3">
-        <v>5.99</v>
+        <v>4</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="8">
+        <v>11.99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C24" s="3">
-        <v>13.99</v>
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="8">
+        <v>15.99</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C25" s="3">
-        <v>11.99</v>
+        <v>4</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="8">
+        <v>12.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" s="3">
-        <v>6.99</v>
+        <v>4</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="8">
+        <v>12.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="3">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="8">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="3">
-        <v>5.99</v>
+        <v>4</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="10">
+        <v>15.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="3">
-        <v>5.99</v>
+        <v>194</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="12">
+        <v>6.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="3">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C31" s="3">
-        <v>15.99</v>
+        <v>194</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" s="14">
+        <v>6.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="3">
-        <v>12.99</v>
+        <v>5</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="16">
+        <v>8.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="3">
-        <v>7.99</v>
+        <v>5</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" s="18">
+        <v>10.99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" s="3">
-        <v>12.99</v>
+        <v>5</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="18">
+        <v>6.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C35" s="3">
-        <v>15.99</v>
+        <v>5</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="18">
+        <v>6.99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" s="3">
-        <v>8.99</v>
+        <v>5</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="18">
+        <v>6.99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C37" s="3">
-        <v>10.99</v>
+        <v>5</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="18">
+        <v>8.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C38" s="3">
+        <v>5</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" s="18">
         <v>6.99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="3">
-        <v>6.99</v>
+        <v>5</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" s="18">
+        <v>9.99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C40" s="3">
-        <v>6.99</v>
+        <v>5</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C40" s="18">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C41" s="3">
-        <v>8.99</v>
+        <v>5</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="18">
+        <v>15.99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C42" s="3">
-        <v>6.99</v>
+        <v>5</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="18">
+        <v>15.99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C43" s="3">
-        <v>4.99</v>
+        <v>5</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="18">
+        <v>6.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C44" s="3">
-        <v>9.99</v>
+        <v>5</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C44" s="18">
+        <v>34.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C45" s="3">
-        <v>17.989999999999998</v>
+        <v>5</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" s="18">
+        <v>11.99</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C46" s="3">
-        <v>15.99</v>
+        <v>5</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" s="18">
+        <v>13.99</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C47" s="3">
-        <v>15.99</v>
+        <v>5</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" s="18">
+        <v>11.99</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C48" s="3">
-        <v>6.99</v>
+        <v>9</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="20">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C49" s="3">
-        <v>34.99</v>
+        <v>9</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="20">
+        <v>6.49</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C50" s="3">
-        <v>11.99</v>
+        <v>9</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="20">
+        <v>5.99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C51" s="3">
-        <v>13.99</v>
+      <c r="C51" s="20">
+        <v>5.99</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" s="3">
-        <v>11.99</v>
+        <v>9</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="20">
+        <v>5.99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="3">
+        <v>20</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="22">
         <v>10.99</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="3">
-        <v>16.989999999999998</v>
+        <v>20</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="22">
+        <v>11.99</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C55" s="5">
-        <v>6.49</v>
+        <v>20</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="22">
+        <v>4.99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C56" s="5">
-        <v>5.99</v>
+        <v>20</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="22">
+        <v>4.99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57">
-        <v>5.99</v>
+        <v>20</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="22">
+        <v>4.99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58">
-        <v>5.99</v>
+      <c r="A58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="24">
+        <v>15.99</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B59" t="s">
-        <v>186</v>
-      </c>
-      <c r="C59">
-        <v>15.99</v>
+        <v>14</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" s="24">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B60" t="s">
-        <v>187</v>
-      </c>
-      <c r="C60">
+        <v>14</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" s="24">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61">
-        <v>6.49</v>
+        <v>14</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="24">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B62" t="s">
-        <v>139</v>
-      </c>
-      <c r="C62">
-        <v>8.99</v>
+        <v>14</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" s="24">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B63" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63">
+        <v>14</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="24">
         <v>6.49</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B64" t="s">
         <v>14</v>
       </c>
-      <c r="C64">
-        <v>6.49</v>
+      <c r="B64" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" s="24">
+        <v>10.99</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65">
-        <v>3.99</v>
+        <v>14</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="24">
+        <v>6.49</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B66" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66">
-        <v>10.99</v>
+        <v>14</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="24">
+        <v>6.49</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67">
-        <v>4.99</v>
+        <v>14</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="24">
+        <v>3.99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B68" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68">
-        <v>11.99</v>
+        <v>26</v>
+      </c>
+      <c r="B68" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" s="26">
+        <v>3.99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69">
-        <v>4.99</v>
+        <v>26</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="26">
+        <v>3.99</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C70" s="7">
-        <v>4.99</v>
+        <v>26</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C70" s="26">
+        <v>3.99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C71" s="7">
-        <v>4.99</v>
+        <v>26</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" s="26">
+        <v>3.99</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
+        <v>26</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C72" s="26">
         <v>3.99</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C73" s="7">
-        <v>3.99</v>
+        <v>26</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="26">
+        <v>5.99</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C74" s="7">
+        <v>26</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="26">
         <v>3.99</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C75" s="7">
-        <v>3.99</v>
+        <v>26</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="28">
+        <v>7.99</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C76" s="7">
+        <v>26</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" s="20">
         <v>3.99</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C77" s="9">
+      <c r="B77" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="30">
         <v>5.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C78">
-        <v>3.99</v>
+      <c r="C78" s="20">
+        <v>26.99</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C79">
-        <v>6.99</v>
+      <c r="C79" s="20">
+        <v>26.99</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C80">
-        <v>3.99</v>
+      <c r="C80" s="20">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B81" t="s">
-        <v>38</v>
-      </c>
-      <c r="C81">
-        <v>6.99</v>
+        <v>173</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" s="20">
+        <v>22.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B82" t="s">
-        <v>39</v>
-      </c>
-      <c r="C82">
-        <v>4.99</v>
+        <v>173</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="20">
+        <v>6.99</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B83" t="s">
-        <v>40</v>
-      </c>
-      <c r="C83">
-        <v>4.99</v>
+        <v>173</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" s="20">
+        <v>7.99</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B84" t="s">
-        <v>41</v>
-      </c>
-      <c r="C84">
-        <v>4.99</v>
+        <v>173</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" s="20">
+        <v>10.99</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B85" t="s">
-        <v>42</v>
-      </c>
-      <c r="C85">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C85" s="20">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86">
-        <v>4.99</v>
+        <v>173</v>
+      </c>
+      <c r="B86" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86" s="30">
+        <v>6.49</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B87" t="s">
-        <v>44</v>
-      </c>
-      <c r="C87">
-        <v>5.99</v>
+        <v>40</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" s="31">
+        <v>6.99</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B88" t="s">
-        <v>45</v>
-      </c>
-      <c r="C88">
-        <v>5.99</v>
+        <v>40</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88" s="31">
+        <v>4.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B89" t="s">
-        <v>31</v>
-      </c>
-      <c r="C89">
-        <v>26.99</v>
+        <v>40</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" s="31">
+        <v>4.99</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C90">
-        <v>26.99</v>
+        <v>40</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90" s="31">
+        <v>4.99</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C91">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C91" s="31">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B92" t="s">
-        <v>34</v>
-      </c>
-      <c r="C92">
-        <v>22.99</v>
+        <v>40</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C92" s="33">
+        <v>5.99</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B93" t="s">
-        <v>35</v>
-      </c>
-      <c r="C93">
+        <v>57</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C93" s="34">
         <v>6.99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B94" t="s">
-        <v>36</v>
-      </c>
-      <c r="C94">
-        <v>6.99</v>
+        <v>57</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C94" s="34">
+        <v>9.99</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B95" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95">
-        <v>6.49</v>
+        <v>57</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C95" s="35">
+        <v>84.99</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B96" t="s">
-        <v>47</v>
-      </c>
-      <c r="C96">
-        <v>3.99</v>
+        <v>57</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C96" s="34">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B97" t="s">
-        <v>48</v>
-      </c>
-      <c r="C97">
+        <v>57</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" s="34">
         <v>6.99</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B98" t="s">
-        <v>192</v>
-      </c>
-      <c r="C98">
+        <v>57</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" s="34">
         <v>6.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B99" t="s">
-        <v>193</v>
-      </c>
-      <c r="C99">
-        <v>9.99</v>
+        <v>57</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" s="34">
+        <v>4.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B100" t="s">
-        <v>49</v>
-      </c>
-      <c r="C100">
-        <v>84.99</v>
+        <v>57</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C100" s="34">
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B101" t="s">
-        <v>50</v>
-      </c>
-      <c r="C101">
-        <v>17.989999999999998</v>
+        <v>57</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C101" s="34">
+        <v>4.99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B102" t="s">
-        <v>51</v>
-      </c>
-      <c r="C102">
-        <v>6.99</v>
+        <v>57</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" s="34">
+        <v>1.99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B103" t="s">
-        <v>52</v>
-      </c>
-      <c r="C103">
-        <v>4.99</v>
+        <v>57</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C103" s="34">
+        <v>2.99</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C104">
-        <v>2.4900000000000002</v>
+        <v>57</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="34">
+        <v>7.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B105" t="s">
-        <v>54</v>
-      </c>
-      <c r="C105">
-        <v>4.99</v>
+        <v>57</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C105" s="34">
+        <v>6.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B106" t="s">
-        <v>55</v>
-      </c>
-      <c r="C106">
+        <v>57</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C106" s="34">
         <v>1.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B107" t="s">
-        <v>56</v>
-      </c>
-      <c r="C107">
-        <v>2.99</v>
+        <v>57</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C107" s="34">
+        <v>1.99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B108" t="s">
         <v>57</v>
       </c>
-      <c r="C108">
-        <v>7.99</v>
+      <c r="B108" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C108" s="34">
+        <v>1.99</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C109">
+        <v>57</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C109" s="34">
         <v>6.99</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B110" t="s">
-        <v>59</v>
-      </c>
-      <c r="C110">
-        <v>1.99</v>
+        <v>57</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C110" s="34">
+        <v>2.99</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B111" t="s">
-        <v>60</v>
-      </c>
-      <c r="C111">
-        <v>1.99</v>
+        <v>57</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C111" s="34">
+        <v>5.99</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B112" t="s">
-        <v>61</v>
-      </c>
-      <c r="C112">
-        <v>1.99</v>
+        <v>57</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112" s="34">
+        <v>3.99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B113" t="s">
-        <v>137</v>
-      </c>
-      <c r="C113">
+        <v>57</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113" s="34">
         <v>6.99</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B114" t="s">
-        <v>62</v>
-      </c>
-      <c r="C114">
-        <v>2.99</v>
+        <v>57</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C114" s="34">
+        <v>9.99</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B115" t="s">
-        <v>63</v>
-      </c>
-      <c r="C115">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C115" s="34">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B116" t="s">
-        <v>64</v>
-      </c>
-      <c r="C116">
+        <v>57</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C116" s="36">
         <v>3.99</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B117" t="s">
-        <v>65</v>
-      </c>
-      <c r="C117">
-        <v>6.99</v>
+        <v>180</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" s="37">
+        <v>5.99</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B118" t="s">
-        <v>194</v>
-      </c>
-      <c r="C118">
-        <v>9.99</v>
+        <v>180</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C118" s="37">
+        <v>4.99</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B119" t="s">
-        <v>195</v>
-      </c>
-      <c r="C119">
-        <v>7.99</v>
+        <v>180</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C119" s="37">
+        <v>0.69</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B120" t="s">
-        <v>196</v>
-      </c>
-      <c r="C120">
+        <v>180</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C120" s="37">
         <v>3.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B121" t="s">
-        <v>197</v>
-      </c>
-      <c r="C121">
-        <v>5.99</v>
+        <v>180</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C121" s="37">
+        <v>6.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B122" t="s">
-        <v>67</v>
-      </c>
-      <c r="C122">
-        <v>4.99</v>
+        <v>180</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C122" s="37">
+        <v>4.49</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B123" t="s">
-        <v>68</v>
-      </c>
-      <c r="C123">
-        <v>0.69</v>
+        <v>180</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C123" s="37">
+        <v>4.49</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B124" t="s">
-        <v>69</v>
-      </c>
-      <c r="C124">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C124" s="37">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B125" t="s">
-        <v>70</v>
-      </c>
-      <c r="C125">
-        <v>6.99</v>
+        <v>180</v>
+      </c>
+      <c r="B125" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C125" s="38">
+        <v>4.99</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B126" t="s">
-        <v>71</v>
-      </c>
-      <c r="C126">
-        <v>4.49</v>
+        <v>101</v>
+      </c>
+      <c r="B126" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C126" s="40">
+        <v>6.99</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B127" t="s">
-        <v>72</v>
-      </c>
-      <c r="C127">
-        <v>4.49</v>
+        <v>101</v>
+      </c>
+      <c r="B127" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C127" s="40">
+        <v>6.99</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B128" t="s">
-        <v>73</v>
-      </c>
-      <c r="C128">
-        <v>4.99</v>
+        <v>101</v>
+      </c>
+      <c r="B128" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C128" s="40">
+        <v>6.99</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B129" t="s">
-        <v>74</v>
-      </c>
-      <c r="C129">
-        <v>6.99</v>
+        <v>101</v>
+      </c>
+      <c r="B129" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C129" s="40">
+        <v>8.49</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B130" t="s">
-        <v>75</v>
-      </c>
-      <c r="C130">
-        <v>6.99</v>
+        <v>101</v>
+      </c>
+      <c r="B130" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C130" s="40">
+        <v>7.99</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B131" t="s">
-        <v>76</v>
-      </c>
-      <c r="C131">
-        <v>6.99</v>
+        <v>101</v>
+      </c>
+      <c r="B131" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C131" s="40">
+        <v>7.99</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B132" t="s">
-        <v>77</v>
-      </c>
-      <c r="C132">
-        <v>8.49</v>
+        <v>101</v>
+      </c>
+      <c r="B132" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C132" s="40">
+        <v>7.99</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B133" t="s">
-        <v>78</v>
-      </c>
-      <c r="C133">
-        <v>7.99</v>
+        <v>101</v>
+      </c>
+      <c r="B133" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C133" s="40">
+        <v>14.99</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B134" t="s">
-        <v>79</v>
-      </c>
-      <c r="C134">
-        <v>7.99</v>
+        <v>101</v>
+      </c>
+      <c r="B134" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C134" s="40">
+        <v>3.99</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B135" t="s">
-        <v>80</v>
-      </c>
-      <c r="C135">
+        <v>101</v>
+      </c>
+      <c r="B135" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="C135" s="40">
         <v>7.99</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B136" t="s">
-        <v>81</v>
-      </c>
-      <c r="C136">
-        <v>14.99</v>
+        <v>101</v>
+      </c>
+      <c r="B136" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C136" s="40">
+        <v>3.99</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B137" t="s">
-        <v>82</v>
-      </c>
-      <c r="C137">
-        <v>3.99</v>
+        <v>101</v>
+      </c>
+      <c r="B137" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="C137" s="40">
+        <v>2.99</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B138" t="s">
-        <v>199</v>
-      </c>
-      <c r="C138">
-        <v>7.99</v>
+        <v>101</v>
+      </c>
+      <c r="B138" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C138" s="40">
+        <v>2.99</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B139" t="s">
-        <v>83</v>
-      </c>
-      <c r="C139">
-        <v>3.99</v>
+        <v>101</v>
+      </c>
+      <c r="B139" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C139" s="40">
+        <v>5.59</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B140" t="s">
-        <v>84</v>
-      </c>
-      <c r="C140">
-        <v>2.99</v>
+        <v>101</v>
+      </c>
+      <c r="B140" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C140" s="40">
+        <v>2.59</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B141" t="s">
-        <v>85</v>
-      </c>
-      <c r="C141">
-        <v>2.99</v>
+        <v>101</v>
+      </c>
+      <c r="B141" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C141" s="40">
+        <v>2.59</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B142" t="s">
-        <v>86</v>
-      </c>
-      <c r="C142">
-        <v>5.59</v>
+        <v>101</v>
+      </c>
+      <c r="B142" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C142" s="40">
+        <v>2.59</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B143" t="s">
-        <v>87</v>
-      </c>
-      <c r="C143">
+        <v>101</v>
+      </c>
+      <c r="B143" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C143" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B144" t="s">
-        <v>88</v>
-      </c>
-      <c r="C144">
+        <v>101</v>
+      </c>
+      <c r="B144" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C144" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B145" t="s">
-        <v>89</v>
-      </c>
-      <c r="C145">
+        <v>101</v>
+      </c>
+      <c r="B145" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C145" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B146" t="s">
-        <v>90</v>
-      </c>
-      <c r="C146">
+        <v>101</v>
+      </c>
+      <c r="B146" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C146" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B147" t="s">
-        <v>91</v>
-      </c>
-      <c r="C147">
+        <v>101</v>
+      </c>
+      <c r="B147" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C147" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B148" t="s">
-        <v>91</v>
-      </c>
-      <c r="C148">
-        <v>2.59</v>
+        <v>101</v>
+      </c>
+      <c r="B148" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C148" s="40">
+        <v>3.99</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B149" t="s">
-        <v>92</v>
-      </c>
-      <c r="C149">
+        <v>101</v>
+      </c>
+      <c r="B149" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C149" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B150" t="s">
-        <v>93</v>
-      </c>
-      <c r="C150">
+        <v>101</v>
+      </c>
+      <c r="B150" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C150" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B151" t="s">
-        <v>94</v>
-      </c>
-      <c r="C151">
-        <v>3.99</v>
+        <v>101</v>
+      </c>
+      <c r="B151" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C151" s="40">
+        <v>1.99</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B152" t="s">
-        <v>95</v>
-      </c>
-      <c r="C152">
+        <v>101</v>
+      </c>
+      <c r="B152" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C152" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B153" t="s">
-        <v>96</v>
-      </c>
-      <c r="C153">
+        <v>101</v>
+      </c>
+      <c r="B153" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C153" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B154" t="s">
-        <v>97</v>
-      </c>
-      <c r="C154">
-        <v>1.99</v>
+        <v>101</v>
+      </c>
+      <c r="B154" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C154" s="40">
+        <v>2.59</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B155" t="s">
-        <v>98</v>
-      </c>
-      <c r="C155">
-        <v>2.59</v>
+        <v>101</v>
+      </c>
+      <c r="B155" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C155" s="40">
+        <v>1.99</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B156" t="s">
-        <v>99</v>
-      </c>
-      <c r="C156">
+        <v>101</v>
+      </c>
+      <c r="B156" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C156" s="40">
         <v>2.59</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B157" t="s">
-        <v>100</v>
-      </c>
-      <c r="C157">
-        <v>2.59</v>
+        <v>101</v>
+      </c>
+      <c r="B157" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C157" s="40">
+        <v>1.99</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B158" t="s">
         <v>101</v>
       </c>
-      <c r="C158">
+      <c r="B158" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C158" s="40">
         <v>1.99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B159" t="s">
-        <v>102</v>
-      </c>
-      <c r="C159">
-        <v>2.59</v>
+        <v>101</v>
+      </c>
+      <c r="B159" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C159" s="40">
+        <v>3.49</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B160" t="s">
-        <v>103</v>
-      </c>
-      <c r="C160">
-        <v>1.99</v>
+        <v>101</v>
+      </c>
+      <c r="B160" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C160" s="40">
+        <v>5.99</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B161" t="s">
-        <v>104</v>
-      </c>
-      <c r="C161">
-        <v>1.99</v>
+        <v>101</v>
+      </c>
+      <c r="B161" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C161" s="40">
+        <v>2.59</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B162" t="s">
-        <v>105</v>
-      </c>
-      <c r="C162">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="B162" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C162" s="40">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B163" t="s">
-        <v>106</v>
-      </c>
-      <c r="C163">
-        <v>5.99</v>
+        <v>101</v>
+      </c>
+      <c r="B163" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C163" s="42">
+        <v>2.59</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B164" t="s">
-        <v>107</v>
-      </c>
-      <c r="C164">
-        <v>2.59</v>
+        <v>124</v>
+      </c>
+      <c r="B164" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C164" s="44">
+        <v>9.99</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B165" t="s">
-        <v>108</v>
-      </c>
-      <c r="C165">
-        <v>2.59</v>
+        <v>124</v>
+      </c>
+      <c r="B165" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="C165" s="46">
+        <v>4.99</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B166" t="s">
-        <v>109</v>
-      </c>
-      <c r="C166">
-        <v>2.59</v>
+        <v>124</v>
+      </c>
+      <c r="B166" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C166" s="46">
+        <v>2.99</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B167" t="s">
-        <v>111</v>
-      </c>
-      <c r="C167">
-        <v>9.99</v>
+        <v>124</v>
+      </c>
+      <c r="B167" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C167" s="47">
+        <v>4.99</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B168" t="s">
-        <v>112</v>
-      </c>
-      <c r="C168">
-        <v>4.99</v>
+        <v>124</v>
+      </c>
+      <c r="B168" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C168" s="46">
+        <v>4.49</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B169" t="s">
-        <v>113</v>
-      </c>
-      <c r="C169">
-        <v>2.99</v>
+        <v>124</v>
+      </c>
+      <c r="B169" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C169" s="46">
+        <v>3.49</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B170" t="s">
-        <v>114</v>
-      </c>
-      <c r="C170">
-        <v>4.99</v>
+        <v>124</v>
+      </c>
+      <c r="B170" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C170" s="46">
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B171" t="s">
-        <v>115</v>
-      </c>
-      <c r="C171">
-        <v>4.49</v>
+        <v>124</v>
+      </c>
+      <c r="B171" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C171" s="46">
+        <v>3.99</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B172" t="s">
-        <v>116</v>
-      </c>
-      <c r="C172">
-        <v>3.49</v>
+        <v>124</v>
+      </c>
+      <c r="B172" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C172" s="46">
+        <v>3.99</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B173" t="s">
-        <v>117</v>
-      </c>
-      <c r="C173">
-        <v>2.4900000000000002</v>
+        <v>124</v>
+      </c>
+      <c r="B173" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C173" s="46">
+        <v>4.99</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B174" t="s">
-        <v>118</v>
-      </c>
-      <c r="C174">
-        <v>3.99</v>
+        <v>124</v>
+      </c>
+      <c r="B174" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C174" s="46">
+        <v>2.99</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B175" t="s">
-        <v>119</v>
-      </c>
-      <c r="C175">
+        <v>124</v>
+      </c>
+      <c r="B175" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C175" s="46">
         <v>3.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B176" t="s">
-        <v>120</v>
-      </c>
-      <c r="C176">
-        <v>4.99</v>
+        <v>124</v>
+      </c>
+      <c r="B176" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C176" s="46">
+        <v>2.99</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B177" t="s">
-        <v>121</v>
-      </c>
-      <c r="C177">
-        <v>2.99</v>
+        <v>124</v>
+      </c>
+      <c r="B177" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C177" s="46">
+        <v>7.99</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B178" t="s">
-        <v>122</v>
-      </c>
-      <c r="C178">
-        <v>3.99</v>
+        <v>124</v>
+      </c>
+      <c r="B178" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C178" s="46">
+        <v>1.99</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B179" t="s">
-        <v>123</v>
-      </c>
-      <c r="C179">
-        <v>2.99</v>
+        <v>124</v>
+      </c>
+      <c r="B179" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C179" s="46">
+        <v>1.99</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B180" t="s">
         <v>124</v>
       </c>
-      <c r="C180">
-        <v>7.99</v>
+      <c r="B180" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C180" s="46">
+        <v>4.49</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B181" t="s">
-        <v>125</v>
-      </c>
-      <c r="C181">
-        <v>1.99</v>
+        <v>124</v>
+      </c>
+      <c r="B181" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C181" s="46">
+        <v>4.49</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B182" t="s">
-        <v>126</v>
-      </c>
-      <c r="C182">
-        <v>1.99</v>
+        <v>124</v>
+      </c>
+      <c r="B182" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C182" s="46">
+        <v>3.49</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B183" t="s">
-        <v>127</v>
-      </c>
-      <c r="C183">
-        <v>4.49</v>
+        <v>124</v>
+      </c>
+      <c r="B183" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C183" s="46">
+        <v>5.99</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B184" t="s">
-        <v>128</v>
-      </c>
-      <c r="C184">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="B184" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C184" s="46">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B185" t="s">
-        <v>129</v>
-      </c>
-      <c r="C185">
-        <v>3.49</v>
+        <v>124</v>
+      </c>
+      <c r="B185" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C185" s="50">
+        <v>4.99</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B186" t="s">
-        <v>130</v>
-      </c>
-      <c r="C186">
+        <v>185</v>
+      </c>
+      <c r="B186" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C186" s="16">
         <v>5.99</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B187" t="s">
-        <v>131</v>
-      </c>
-      <c r="C187">
-        <v>6.99</v>
+        <v>185</v>
+      </c>
+      <c r="B187" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C187" s="18">
+        <v>9.99</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B188" t="s">
-        <v>132</v>
-      </c>
-      <c r="C188">
-        <v>4.99</v>
+        <v>185</v>
+      </c>
+      <c r="B188" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C188" s="18">
+        <v>3.49</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B189" t="s">
-        <v>200</v>
-      </c>
-      <c r="C189">
-        <v>5.99</v>
+        <v>185</v>
+      </c>
+      <c r="B189" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C189" s="18">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B190" t="s">
-        <v>201</v>
-      </c>
-      <c r="C190">
-        <v>9.99</v>
+        <v>205</v>
+      </c>
+      <c r="B190" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C190" s="20">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B191" t="s">
-        <v>202</v>
-      </c>
-      <c r="C191">
-        <v>3.49</v>
+        <v>205</v>
+      </c>
+      <c r="B191" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C191" s="20">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B192" t="s">
-        <v>141</v>
-      </c>
-      <c r="C192">
-        <v>19.989999999999998</v>
+        <v>205</v>
+      </c>
+      <c r="B192" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C192" s="20">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B193" t="s">
-        <v>204</v>
-      </c>
-      <c r="C193">
-        <v>19.989999999999998</v>
+      <c r="B193" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C193" s="20">
+        <v>20.99</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B194" t="s">
-        <v>134</v>
-      </c>
-      <c r="C194">
-        <v>18.989999999999998</v>
+      <c r="B194" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C194" s="20">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B195" t="s">
-        <v>135</v>
-      </c>
-      <c r="C195">
-        <v>20.99</v>
-      </c>
+      <c r="A195" s="4"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B196" t="s">
-        <v>136</v>
-      </c>
-      <c r="C196">
-        <v>16.989999999999998</v>
-      </c>
+      <c r="A196" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/Menu.xlsx
+++ b/public/Menu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76649709-73EA-43C2-A12F-22045A17EBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442292FB-877E-44E4-8EC3-F9D1E15436C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="205">
   <si>
     <t>Category</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Koral Fish (Steak - head&amp;tail excluded) - 2lb</t>
-  </si>
-  <si>
     <t>Frozen Fish</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>Dried Fish</t>
   </si>
   <si>
-    <t>Loita Shutki Bhorta</t>
-  </si>
-  <si>
     <t>Kothbel Bhorta 200gm</t>
   </si>
   <si>
@@ -70,9 +64,6 @@
     <t>PLAIN PARATHA 30PACK</t>
   </si>
   <si>
-    <t>Vegetable Singara Family Pack (25 Pieces)</t>
-  </si>
-  <si>
     <t>Vegetable Samosa</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>Bombay Chanachur (Regular)</t>
   </si>
   <si>
-    <t>Ruchi BBQ Chanachur 300gm</t>
-  </si>
-  <si>
     <t>Dry Cake</t>
   </si>
   <si>
@@ -424,18 +412,12 @@
     <t>Rui Fish 3KG+ (Cut &amp; Desclaed)</t>
   </si>
   <si>
-    <t>Chitol Fish (2/3KG) - Cut</t>
-  </si>
-  <si>
     <t>Hilsha Fish 1000gm++ - Cut</t>
   </si>
   <si>
     <t>Hilsha Egg</t>
   </si>
   <si>
-    <t>Hilsha Fish 2 pack - Large</t>
-  </si>
-  <si>
     <t>Batashi Fish 500gm</t>
   </si>
   <si>
@@ -466,18 +448,9 @@
     <t>Pabda Fish 500gm</t>
   </si>
   <si>
-    <t>Shing Fish 500gm</t>
-  </si>
-  <si>
     <t>Tengra 500gm</t>
   </si>
   <si>
-    <t>Local Beef (approx. 2.5lb pack)</t>
-  </si>
-  <si>
-    <t>Boneless Beef (approx. 2.5lb pack)</t>
-  </si>
-  <si>
     <t>Beef liver (approx. 2lb pack)</t>
   </si>
   <si>
@@ -487,9 +460,6 @@
     <t>Beef Kidney</t>
   </si>
   <si>
-    <t>Beef Steak</t>
-  </si>
-  <si>
     <t>Ground Beef (approx. 1lb Pack)</t>
   </si>
   <si>
@@ -529,9 +499,6 @@
     <t>Premium Sweets - Morog Pulao</t>
   </si>
   <si>
-    <t>Premium Sweets - Kacchi Biriyani</t>
-  </si>
-  <si>
     <t>Frozen Data 300gm</t>
   </si>
   <si>
@@ -583,9 +550,6 @@
     <t>Premium Sweets - Khirsha Doi</t>
   </si>
   <si>
-    <t>Rui Fish 5KG+ - Cut (Can be taken full or half)</t>
-  </si>
-  <si>
     <t>Katla Fish 5KG+ - Cut (Can be taken full or half)</t>
   </si>
   <si>
@@ -604,18 +568,6 @@
     <t>Meni Fish 500gm</t>
   </si>
   <si>
-    <t>Fresh Vegetables &amp; Fruits</t>
-  </si>
-  <si>
-    <t>Potol</t>
-  </si>
-  <si>
-    <t>Fazli Aam</t>
-  </si>
-  <si>
-    <t>Zara Lebu</t>
-  </si>
-  <si>
     <t>Premium Sweets - Assorted Laddu</t>
   </si>
   <si>
@@ -634,10 +586,55 @@
     <t>Cocola Noodles</t>
   </si>
   <si>
-    <t>Hot Chanachur</t>
-  </si>
-  <si>
     <t>Deshi Sweets</t>
+  </si>
+  <si>
+    <t>Hilsha Fish 1500gm+ - Cut</t>
+  </si>
+  <si>
+    <t>Chitol Fish (3KG) - Cut</t>
+  </si>
+  <si>
+    <t>Shoil Fish (1.5KG+) - Cut</t>
+  </si>
+  <si>
+    <t>Shorputi (1.5KG+) - Cut</t>
+  </si>
+  <si>
+    <t>Koi Fish 1 KG</t>
+  </si>
+  <si>
+    <t>Local Beef (approx. 3lb pack)</t>
+  </si>
+  <si>
+    <t>Mutton (Goat) - Approx. 3lb Pack - Kacchi Cut</t>
+  </si>
+  <si>
+    <t>Cocktail Snack (Dal puri, Singara, Samosa, Naga Spring Roll)</t>
+  </si>
+  <si>
+    <t>Kochur Loti</t>
+  </si>
+  <si>
+    <t>Frozen Satkora</t>
+  </si>
+  <si>
+    <t>Frozen Drumstick (সজনে ডাটা)</t>
+  </si>
+  <si>
+    <t>Frozen Green Chili (কাচা মরিচ)</t>
+  </si>
+  <si>
+    <t>Nicobena Mango Pickle</t>
+  </si>
+  <si>
+    <t>Rice Flour 2lb</t>
+  </si>
+  <si>
+    <t>Banaful Hot Chanachur</t>
+  </si>
+  <si>
+    <t>Banaful BBQ Chanachur 300gm</t>
   </si>
 </sst>
 </file>
@@ -647,7 +644,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,8 +666,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,8 +687,56 @@
         <bgColor rgb="FF667EEA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor theme="7" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor theme="8" tint="-0.249977111117893"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="44">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1255,11 +1307,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,88 +1358,133 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1660,12 +1787,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D196"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="49.33203125" style="47" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" style="47" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1682,10 +1809,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C2" s="8">
         <v>24.99</v>
@@ -1694,10 +1821,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C3" s="8">
         <v>42.99</v>
@@ -1706,34 +1833,32 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="C4" s="8">
-        <v>79.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="8">
-        <v>89.99</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C6" s="8">
         <v>10.99</v>
@@ -1742,10 +1867,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="C7" s="8">
         <v>54.99</v>
@@ -1754,10 +1879,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C8" s="8">
         <v>32.99</v>
@@ -1765,153 +1890,153 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="C9" s="8">
-        <v>37.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="C10" s="8">
-        <v>16.989999999999998</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C11" s="8">
-        <v>26.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="C12" s="8">
-        <v>12.99</v>
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C13" s="8">
-        <v>13.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="C14" s="8">
-        <v>16.989999999999998</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="C15" s="8">
-        <v>5.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C16" s="8">
-        <v>12.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C17" s="8">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C18" s="8">
-        <v>13.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C19" s="8">
-        <v>6.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="C20" s="8">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="C21" s="8">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C22" s="8">
         <v>5.99</v>
@@ -1919,43 +2044,43 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C23" s="8">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C24" s="8">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C25" s="8">
-        <v>12.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C26" s="8">
         <v>12.99</v>
@@ -1963,10 +2088,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C27" s="8">
         <v>12.99</v>
@@ -1974,10 +2099,10 @@
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C28" s="10">
         <v>15.99</v>
@@ -1985,32 +2110,32 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>194</v>
+        <v>3</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="C29" s="12">
-        <v>6.99</v>
+        <v>89.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>196</v>
-      </c>
       <c r="C30" s="12">
-        <v>40</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>194</v>
+        <v>4</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="C31" s="14">
         <v>6.99</v>
@@ -2018,32 +2143,32 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C32" s="16">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C33" s="18">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C34" s="18">
         <v>6.99</v>
@@ -2051,120 +2176,120 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C35" s="18">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C36" s="18">
-        <v>6.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C37" s="18">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C38" s="18">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C39" s="18">
-        <v>9.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C40" s="18">
-        <v>17.989999999999998</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C41" s="18">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C42" s="18">
-        <v>15.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C43" s="18">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="C44" s="18">
-        <v>34.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C45" s="18">
         <v>11.99</v>
@@ -2172,54 +2297,54 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B46" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="18">
-        <v>13.99</v>
+      <c r="C46" s="20">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="C47" s="18">
-        <v>11.99</v>
+        <v>8</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="20">
+        <v>6.49</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="C48" s="20">
-        <v>16.989999999999998</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>166</v>
+        <v>6</v>
       </c>
       <c r="C49" s="20">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="C50" s="20">
         <v>5.99</v>
@@ -2227,208 +2352,208 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="20">
-        <v>5.99</v>
+        <v>17</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="22">
+        <v>10.99</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="20">
-        <v>5.99</v>
+        <v>17</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" s="22">
+        <v>11.99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" s="22">
-        <v>10.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" s="22">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C55" s="22">
         <v>4.99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="22">
-        <v>4.99</v>
+      <c r="A56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="37">
+        <v>15.99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" s="22">
-        <v>4.99</v>
+      <c r="A57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" s="24">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="C58" s="24">
-        <v>15.99</v>
+        <v>12</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="37">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C59" s="24">
-        <v>19.989999999999998</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="C60" s="24">
-        <v>19.989999999999998</v>
+        <v>12</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" s="37">
+        <v>10.99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="C61" s="24">
-        <v>16.989999999999998</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B62" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C62" s="24">
-        <v>16.989999999999998</v>
+        <v>12</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="37">
+        <v>6.49</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C63" s="24">
-        <v>6.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B64" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C64" s="24">
-        <v>10.99</v>
+        <v>23</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="39">
+        <v>3.99</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B65" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="24">
-        <v>6.49</v>
+        <v>23</v>
+      </c>
+      <c r="B65" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" s="26">
+        <v>3.99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="24">
-        <v>6.49</v>
+        <v>23</v>
+      </c>
+      <c r="B66" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="39">
+        <v>3.99</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="24">
+        <v>23</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="26">
         <v>3.99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B68" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68" s="26">
+        <v>23</v>
+      </c>
+      <c r="B68" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="39">
         <v>3.99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="C69" s="26">
         <v>3.99</v>
@@ -2436,1286 +2561,1286 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B70" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="C70" s="26">
-        <v>3.99</v>
+        <v>23</v>
+      </c>
+      <c r="B70" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="39">
+        <v>5.99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="C71" s="26">
         <v>3.99</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C72" s="26">
+        <v>23</v>
+      </c>
+      <c r="B72" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="42">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C73" s="43">
         <v>3.99</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B73" s="25" t="s">
+    <row r="74" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="26">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="26">
+      <c r="B74" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="44">
         <v>3.99</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C75" s="28">
-        <v>7.99</v>
+        <v>23</v>
+      </c>
+      <c r="B75" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="C75" s="43">
+        <v>3.99</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="C76" s="20">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B77" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="30">
-        <v>5.99</v>
+        <v>162</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="20">
+        <v>26.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C78" s="20">
-        <v>26.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C79" s="20">
-        <v>26.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C80" s="20">
-        <v>16.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="C81" s="20">
-        <v>22.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="C82" s="20">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="C83" s="20">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C84" s="20">
-        <v>10.99</v>
+        <v>162</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="29">
+        <v>6.49</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B85" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="30">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B86" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C85" s="20">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B86" s="29" t="s">
-        <v>33</v>
-      </c>
       <c r="C86" s="30">
-        <v>6.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87" s="31">
-        <v>6.99</v>
+        <v>33</v>
+      </c>
+      <c r="C87" s="30">
+        <v>4.99</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C88" s="31">
+        <v>34</v>
+      </c>
+      <c r="C88" s="30">
         <v>4.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B89" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" s="30">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C89" s="31">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B90" s="21" t="s">
+      <c r="C90" s="32">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="31">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B91" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C91" s="31">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="C91" s="32">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B92" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C92" s="33">
-        <v>5.99</v>
+        <v>54</v>
+      </c>
+      <c r="B92" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="48">
+        <v>6.99</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C93" s="34">
-        <v>6.99</v>
+        <v>164</v>
+      </c>
+      <c r="C93" s="33">
+        <v>9.99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C94" s="34">
-        <v>9.99</v>
+        <v>54</v>
+      </c>
+      <c r="B94" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94" s="49">
+        <v>84.99</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C95" s="35">
-        <v>84.99</v>
+        <v>39</v>
+      </c>
+      <c r="C95" s="33">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C96" s="34">
-        <v>17.989999999999998</v>
+        <v>54</v>
+      </c>
+      <c r="B96" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C96" s="48">
+        <v>6.99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C97" s="34">
+        <v>186</v>
+      </c>
+      <c r="C97" s="33">
         <v>6.99</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B98" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B98" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="34">
-        <v>6.99</v>
+      <c r="C98" s="48">
+        <v>4.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C99" s="34">
+        <v>41</v>
+      </c>
+      <c r="C99" s="33">
         <v>4.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C100" s="34">
+        <v>54</v>
+      </c>
+      <c r="B100" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="C100" s="48">
         <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C101" s="34">
+        <v>42</v>
+      </c>
+      <c r="C101" s="33">
         <v>4.99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C102" s="34">
+        <v>54</v>
+      </c>
+      <c r="B102" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C102" s="48">
         <v>1.99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C103" s="34">
+        <v>44</v>
+      </c>
+      <c r="C103" s="33">
         <v>2.99</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C104" s="34">
+        <v>54</v>
+      </c>
+      <c r="B104" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C104" s="48">
         <v>7.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C105" s="34">
+        <v>46</v>
+      </c>
+      <c r="C105" s="33">
         <v>6.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C106" s="34">
+        <v>54</v>
+      </c>
+      <c r="B106" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" s="48">
         <v>1.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C107" s="34">
+        <v>48</v>
+      </c>
+      <c r="C107" s="33">
         <v>1.99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C108" s="34">
+        <v>54</v>
+      </c>
+      <c r="B108" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C108" s="48">
         <v>1.99</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C109" s="34">
+        <v>124</v>
+      </c>
+      <c r="C109" s="33">
         <v>6.99</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C110" s="34">
+        <v>54</v>
+      </c>
+      <c r="B110" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C110" s="48">
         <v>2.99</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C111" s="34">
+        <v>51</v>
+      </c>
+      <c r="C111" s="33">
         <v>5.99</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C112" s="34">
+        <v>54</v>
+      </c>
+      <c r="B112" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C112" s="48">
         <v>3.99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C113" s="34">
+        <v>53</v>
+      </c>
+      <c r="C113" s="33">
         <v>6.99</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C114" s="34">
+        <v>54</v>
+      </c>
+      <c r="B114" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C114" s="48">
         <v>9.99</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C115" s="34">
+        <v>166</v>
+      </c>
+      <c r="C115" s="33">
         <v>7.99</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C116" s="36">
+        <v>54</v>
+      </c>
+      <c r="B116" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C116" s="51">
         <v>3.99</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C117" s="37">
+        <v>169</v>
+      </c>
+      <c r="B117" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C117" s="53">
         <v>5.99</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C118" s="37">
+        <v>55</v>
+      </c>
+      <c r="C118" s="34">
         <v>4.99</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B119" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C119" s="37">
+        <v>169</v>
+      </c>
+      <c r="B119" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" s="53">
         <v>0.69</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C120" s="37">
+        <v>57</v>
+      </c>
+      <c r="C120" s="34">
         <v>3.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C121" s="37">
+        <v>169</v>
+      </c>
+      <c r="B121" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C121" s="53">
         <v>6.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C122" s="37">
+        <v>59</v>
+      </c>
+      <c r="C122" s="34">
         <v>4.49</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C123" s="37">
+        <v>169</v>
+      </c>
+      <c r="B123" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="C123" s="53">
         <v>4.49</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C124" s="37">
+        <v>204</v>
+      </c>
+      <c r="C124" s="34">
         <v>4.49</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B125" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C125" s="38">
+        <v>169</v>
+      </c>
+      <c r="B125" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C125" s="55">
         <v>4.99</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B126" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="C126" s="40">
+        <v>97</v>
+      </c>
+      <c r="B126" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C126" s="57">
         <v>6.99</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B127" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C127" s="40">
+        <v>97</v>
+      </c>
+      <c r="B127" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="C127" s="59">
         <v>6.99</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B128" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="C128" s="40">
+        <v>97</v>
+      </c>
+      <c r="B128" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C128" s="57">
         <v>6.99</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B129" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C129" s="40">
+        <v>97</v>
+      </c>
+      <c r="B129" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C129" s="59">
         <v>8.49</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B130" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="C130" s="40">
+        <v>97</v>
+      </c>
+      <c r="B130" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="C130" s="57">
         <v>7.99</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B131" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C131" s="40">
+        <v>97</v>
+      </c>
+      <c r="B131" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="C131" s="59">
         <v>7.99</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B132" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C132" s="40">
+        <v>97</v>
+      </c>
+      <c r="B132" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C132" s="57">
         <v>7.99</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B133" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C133" s="40">
+        <v>97</v>
+      </c>
+      <c r="B133" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C133" s="59">
         <v>14.99</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B134" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C134" s="40">
+        <v>97</v>
+      </c>
+      <c r="B134" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C134" s="57">
         <v>3.99</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B135" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="C135" s="40">
+        <v>97</v>
+      </c>
+      <c r="B135" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="C135" s="59">
         <v>7.99</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B136" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C136" s="40">
+        <v>97</v>
+      </c>
+      <c r="B136" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C136" s="57">
         <v>3.99</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B137" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C137" s="40">
+        <v>97</v>
+      </c>
+      <c r="B137" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="C137" s="59">
         <v>2.99</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B138" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="C138" s="40">
+        <v>97</v>
+      </c>
+      <c r="B138" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C138" s="57">
         <v>2.99</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B139" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C139" s="40">
+        <v>97</v>
+      </c>
+      <c r="B139" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C139" s="59">
         <v>5.59</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B140" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C140" s="40">
+        <v>97</v>
+      </c>
+      <c r="B140" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C140" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B141" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C141" s="40">
+        <v>97</v>
+      </c>
+      <c r="B141" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C141" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B142" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C142" s="40">
+        <v>97</v>
+      </c>
+      <c r="B142" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C142" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B143" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C143" s="40">
+        <v>97</v>
+      </c>
+      <c r="B143" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C143" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B144" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C144" s="40">
+        <v>97</v>
+      </c>
+      <c r="B144" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C144" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B145" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C145" s="40">
+        <v>97</v>
+      </c>
+      <c r="B145" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B146" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C146" s="40">
+        <v>97</v>
+      </c>
+      <c r="B146" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C146" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B147" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C147" s="40">
+        <v>97</v>
+      </c>
+      <c r="B147" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C147" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B148" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C148" s="40">
+        <v>97</v>
+      </c>
+      <c r="B148" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="C148" s="57">
         <v>3.99</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B149" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C149" s="40">
+        <v>97</v>
+      </c>
+      <c r="B149" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C149" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B150" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C150" s="40">
+        <v>97</v>
+      </c>
+      <c r="B150" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C150" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B151" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C151" s="40">
+        <v>97</v>
+      </c>
+      <c r="B151" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="C151" s="59">
         <v>1.99</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B152" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C152" s="40">
+        <v>97</v>
+      </c>
+      <c r="B152" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C152" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B153" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="C153" s="40">
+        <v>97</v>
+      </c>
+      <c r="B153" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="C153" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B154" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C154" s="40">
+        <v>97</v>
+      </c>
+      <c r="B154" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="C154" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B155" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C155" s="40">
+        <v>97</v>
+      </c>
+      <c r="B155" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C155" s="59">
         <v>1.99</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B156" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C156" s="40">
+        <v>97</v>
+      </c>
+      <c r="B156" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="C156" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B157" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C157" s="40">
+        <v>97</v>
+      </c>
+      <c r="B157" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C157" s="59">
         <v>1.99</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B158" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="C158" s="40">
+        <v>97</v>
+      </c>
+      <c r="B158" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C158" s="57">
         <v>1.99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B159" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C159" s="40">
-        <v>3.49</v>
+        <v>97</v>
+      </c>
+      <c r="B159" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="C159" s="59">
+        <v>4.99</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B160" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="C160" s="40">
+      <c r="B160" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="C160" s="57">
         <v>5.99</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B161" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C161" s="40">
+        <v>97</v>
+      </c>
+      <c r="B161" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C161" s="59">
         <v>2.59</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B162" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C162" s="40">
+        <v>97</v>
+      </c>
+      <c r="B162" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C162" s="57">
         <v>2.59</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B163" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="C163" s="42">
+        <v>97</v>
+      </c>
+      <c r="B163" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="C163" s="61">
         <v>2.59</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B164" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C164" s="44">
-        <v>9.99</v>
+        <v>120</v>
+      </c>
+      <c r="B164" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="C164" s="63">
+        <v>11.99</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B165" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="C165" s="46">
+        <v>120</v>
+      </c>
+      <c r="B165" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C165" s="65">
         <v>4.99</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B166" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C166" s="46">
+        <v>120</v>
+      </c>
+      <c r="B166" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="C166" s="67">
         <v>2.99</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B167" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C167" s="47">
+        <v>120</v>
+      </c>
+      <c r="B167" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="C167" s="68">
         <v>4.99</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B168" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="C168" s="46">
+        <v>120</v>
+      </c>
+      <c r="B168" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C168" s="67">
         <v>4.49</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B169" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="C169" s="46">
+        <v>120</v>
+      </c>
+      <c r="B169" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="C169" s="65">
         <v>3.49</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B170" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="C170" s="46">
+        <v>120</v>
+      </c>
+      <c r="B170" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C170" s="67">
         <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B171" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C171" s="46">
+        <v>120</v>
+      </c>
+      <c r="B171" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C171" s="65">
         <v>3.99</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B172" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C172" s="46">
+        <v>120</v>
+      </c>
+      <c r="B172" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="C172" s="67">
         <v>3.99</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B173" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="C173" s="46">
+        <v>120</v>
+      </c>
+      <c r="B173" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="C173" s="65">
         <v>4.99</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B174" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C174" s="46">
+        <v>120</v>
+      </c>
+      <c r="B174" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="C174" s="67">
         <v>2.99</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B175" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="C175" s="46">
+        <v>120</v>
+      </c>
+      <c r="B175" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="C175" s="65">
         <v>3.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B176" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C176" s="46">
+        <v>120</v>
+      </c>
+      <c r="B176" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C176" s="67">
         <v>2.99</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B177" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C177" s="46">
+        <v>120</v>
+      </c>
+      <c r="B177" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="C177" s="65">
         <v>7.99</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B178" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C178" s="46">
+        <v>120</v>
+      </c>
+      <c r="B178" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="C178" s="67">
         <v>1.99</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B179" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C179" s="46">
+        <v>120</v>
+      </c>
+      <c r="B179" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C179" s="65">
         <v>1.99</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B180" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C180" s="46">
+        <v>120</v>
+      </c>
+      <c r="B180" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C180" s="67">
         <v>4.49</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B181" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C181" s="46">
+        <v>120</v>
+      </c>
+      <c r="B181" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C181" s="65">
         <v>4.49</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B182" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="C182" s="46">
+      <c r="B182" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="C182" s="67">
         <v>3.49</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B183" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C183" s="46">
+        <v>120</v>
+      </c>
+      <c r="B183" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="C183" s="65">
         <v>5.99</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B184" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C184" s="46">
+        <v>120</v>
+      </c>
+      <c r="B184" s="66" t="s">
+        <v>118</v>
+      </c>
+      <c r="C184" s="67">
         <v>6.99</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B185" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="C185" s="50">
+        <v>120</v>
+      </c>
+      <c r="B185" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="C185" s="72">
         <v>4.99</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C186" s="16">
         <v>5.99</v>
@@ -3723,10 +3848,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C187" s="18">
         <v>9.99</v>
@@ -3734,10 +3859,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B188" s="51" t="s">
-        <v>184</v>
+        <v>174</v>
+      </c>
+      <c r="B188" s="35" t="s">
+        <v>173</v>
       </c>
       <c r="C188" s="18">
         <v>3.49</v>
@@ -3745,10 +3870,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C189" s="18">
         <v>19.989999999999998</v>
@@ -3756,10 +3881,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B190" s="19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C190" s="20">
         <v>19.989999999999998</v>
@@ -3767,10 +3892,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B191" s="19" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C191" s="20">
         <v>16.989999999999998</v>
@@ -3778,10 +3903,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B192" s="19" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C192" s="20">
         <v>18.989999999999998</v>
@@ -3789,10 +3914,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B193" s="19" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C193" s="20">
         <v>20.99</v>
@@ -3800,20 +3925,20 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B194" s="19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C194" s="20">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="4"/>
-    </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="4"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
